--- a/artfynd/A 56183-2022 artfynd.xlsx
+++ b/artfynd/A 56183-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 56183-2022 artfynd.xlsx
+++ b/artfynd/A 56183-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104449339</v>
+        <v>114019680</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,45 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännvallen, Jmt</t>
+          <t>Ängesvallen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>418114.5890296631</v>
+        <v>418081</v>
       </c>
       <c r="R2" t="n">
-        <v>7018307.562617064</v>
+        <v>7018162</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>ringhack</t>
+          <t>2024-01-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Rashid Kadhim</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104449296</v>
+        <v>104449387</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,42 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>418020.8466201274</v>
+        <v>418160</v>
       </c>
       <c r="R3" t="n">
-        <v>7018290.5937497</v>
+        <v>7018308</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,24 +844,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -925,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104449303</v>
+        <v>104449390</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -941,42 +884,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>417968.3300327867</v>
+        <v>418166</v>
       </c>
       <c r="R4" t="n">
-        <v>7018811.828307464</v>
+        <v>7018080</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,24 +941,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,15 +970,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104449341</v>
+        <v>104449393</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,42 +981,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>418102.9833736739</v>
+        <v>418189</v>
       </c>
       <c r="R5" t="n">
-        <v>7018294.353320676</v>
+        <v>7018073</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1131,24 +1038,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,15 +1067,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104449347</v>
+        <v>104449292</v>
       </c>
       <c r="B6" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1213,7 +1100,7 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1223,10 +1110,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>418120.6552801228</v>
+        <v>418038</v>
       </c>
       <c r="R6" t="n">
-        <v>7018244.835489267</v>
+        <v>7018281</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,19 +1143,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1300,15 +1177,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104449299</v>
+        <v>104449293</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1348,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>418112.8997429173</v>
+        <v>418014</v>
       </c>
       <c r="R7" t="n">
-        <v>7018754.582477763</v>
+        <v>7018281</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1381,19 +1253,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1425,15 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>104449353</v>
+        <v>104449294</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1473,10 +1330,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>418127.046540436</v>
+        <v>418015</v>
       </c>
       <c r="R8" t="n">
-        <v>7018124.025634385</v>
+        <v>7018290</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1506,19 +1363,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1550,15 +1397,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>104449336</v>
+        <v>104449295</v>
       </c>
       <c r="B9" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1598,10 +1440,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>418140.5297435718</v>
+        <v>418006</v>
       </c>
       <c r="R9" t="n">
-        <v>7018317.255908524</v>
+        <v>7018300</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1631,19 +1473,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1675,15 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>104449350</v>
+        <v>104449296</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1723,10 +1550,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>418122.010810772</v>
+        <v>418021</v>
       </c>
       <c r="R10" t="n">
-        <v>7018121.002526658</v>
+        <v>7018290</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1756,19 +1583,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1800,15 +1617,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>104449294</v>
+        <v>104449299</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1838,7 +1650,7 @@
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1848,10 +1660,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>418014.9559451528</v>
+        <v>418113</v>
       </c>
       <c r="R11" t="n">
-        <v>7018289.393415486</v>
+        <v>7018754</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1881,19 +1693,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1925,15 +1727,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>104449356</v>
+        <v>104449300</v>
       </c>
       <c r="B12" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1973,10 +1770,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>418167.5659540299</v>
+        <v>417939</v>
       </c>
       <c r="R12" t="n">
-        <v>7018086.529375146</v>
+        <v>7018810</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2006,19 +1803,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -2050,15 +1837,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>104449398</v>
+        <v>104449301</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2066,34 +1848,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>417951.0739390327</v>
+        <v>417955</v>
       </c>
       <c r="R13" t="n">
-        <v>7018824.420966904</v>
+        <v>7018806</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2123,19 +1913,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2162,15 +1947,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>104449390</v>
+        <v>104449302</v>
       </c>
       <c r="B14" t="n">
-        <v>78570</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2178,34 +1958,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>418166.4817944319</v>
+        <v>417964</v>
       </c>
       <c r="R14" t="n">
-        <v>7018079.353921369</v>
+        <v>7018823</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2235,19 +2023,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2274,15 +2057,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>104449344</v>
+        <v>104449303</v>
       </c>
       <c r="B15" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2312,7 +2090,7 @@
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
@@ -2322,10 +2100,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>418107.3009797331</v>
+        <v>417968</v>
       </c>
       <c r="R15" t="n">
-        <v>7018251.477823625</v>
+        <v>7018812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2355,19 +2133,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2402,12 +2170,7 @@
         <v>104449304</v>
       </c>
       <c r="B16" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2447,10 +2210,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>418063.1796718984</v>
+        <v>418063</v>
       </c>
       <c r="R16" t="n">
-        <v>7018819.762094007</v>
+        <v>7018820</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2480,19 +2243,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2524,15 +2277,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>104449302</v>
+        <v>104449305</v>
       </c>
       <c r="B17" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2572,10 +2320,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>417964.1242904485</v>
+        <v>418113</v>
       </c>
       <c r="R17" t="n">
-        <v>7018823.637913963</v>
+        <v>7018905</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2605,19 +2353,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
@@ -2649,15 +2387,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>104449293</v>
+        <v>104449306</v>
       </c>
       <c r="B18" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2697,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>418013.8256269969</v>
+        <v>418116</v>
       </c>
       <c r="R18" t="n">
-        <v>7018280.418971322</v>
+        <v>7018906</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2730,19 +2463,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2774,15 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>104449292</v>
+        <v>104449307</v>
       </c>
       <c r="B19" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2822,10 +2540,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>418038.1746898587</v>
+        <v>418106</v>
       </c>
       <c r="R19" t="n">
-        <v>7018280.698708942</v>
+        <v>7018911</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2855,19 +2573,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2899,15 +2607,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>104449300</v>
+        <v>104449336</v>
       </c>
       <c r="B20" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2947,10 +2650,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>417939.4464318861</v>
+        <v>418141</v>
       </c>
       <c r="R20" t="n">
-        <v>7018810.314819056</v>
+        <v>7018317</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2980,19 +2683,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -3024,15 +2717,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>104449295</v>
+        <v>104449339</v>
       </c>
       <c r="B21" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3062,7 +2750,7 @@
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -3072,10 +2760,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>418005.7710606223</v>
+        <v>418115</v>
       </c>
       <c r="R21" t="n">
-        <v>7018300.431433921</v>
+        <v>7018308</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3105,19 +2793,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
@@ -3149,15 +2827,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>104449301</v>
+        <v>104449341</v>
       </c>
       <c r="B22" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3187,7 +2860,7 @@
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
@@ -3197,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>417955.5464219641</v>
+        <v>418103</v>
       </c>
       <c r="R22" t="n">
-        <v>7018805.403093246</v>
+        <v>7018295</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3230,19 +2903,9 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-11-02</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
@@ -3274,15 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>104449399</v>
+        <v>104449344</v>
       </c>
       <c r="B23" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3290,34 +2948,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>417961.3644657138</v>
+        <v>418107</v>
       </c>
       <c r="R23" t="n">
-        <v>7018821.457881615</v>
+        <v>7018252</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3347,19 +3013,14 @@
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-11-02</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3386,15 +3047,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>114019680</v>
+        <v>104449347</v>
       </c>
       <c r="B24" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3402,40 +3058,45 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ängesvallen, Jmt</t>
+          <t>Brännvallen, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>418081</v>
+        <v>418120</v>
       </c>
       <c r="R24" t="n">
-        <v>7018162</v>
+        <v>7018245</v>
       </c>
       <c r="S24" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3459,12 +3120,17 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2022-11-02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-01-10</t>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3473,22 +3139,460 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Benny Öwre</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>104449350</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>418122</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7018121</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>104449353</v>
+      </c>
+      <c r="B26" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>418127</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7018124</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>104449356</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>418167</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7018086</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>ringhack</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>104449396</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58057</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Brännvallen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>418159</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7018046</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Undersåker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2022-11-02</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 56183-2022 artfynd.xlsx
+++ b/artfynd/A 56183-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/114019680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449393</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1174,6 +1199,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449292</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449293</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1394,6 +1429,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449294</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1504,6 +1544,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449295</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449296</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1724,6 +1774,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449299</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1834,6 +1889,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449300</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1944,6 +2004,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449301</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2054,6 +2119,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449302</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2164,6 +2234,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449303</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2274,6 +2349,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449304</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2384,6 +2464,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449305</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2494,6 +2579,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449306</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2604,6 +2694,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449307</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2714,6 +2809,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449336</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2824,6 +2924,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449339</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2934,6 +3039,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449341</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3044,6 +3154,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449344</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3154,6 +3269,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449347</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3264,6 +3384,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449350</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3374,6 +3499,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449353</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3484,6 +3614,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449356</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3593,8 +3728,42 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104449396</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>